--- a/ttl_long/AdHoc_Net_12.xlsx
+++ b/ttl_long/AdHoc_Net_12.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>313</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>69</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>337</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>157</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>211</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>313</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>317</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>335</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>339</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>369</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>410</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>518</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>247</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>569</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>520</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>632</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>710</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>630</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>807</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>792</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>870</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>873</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>890</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>975</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1007</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>331</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1013</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1046</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>230</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1093</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1116</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,233 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1233</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1511</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1532</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1565</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1599</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1057,7 +1278,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1079,7 +1300,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1101,7 +1322,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1123,7 +1344,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1145,7 +1366,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1167,7 +1388,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1189,7 +1410,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1211,7 +1432,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1233,7 +1454,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1272,12 +1493,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1299,7 +1520,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1321,7 +1542,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1338,12 +1559,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1382,12 +1603,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1404,12 +1625,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1426,12 +1647,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1448,12 +1669,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1470,12 +1691,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1492,12 +1713,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1514,12 +1735,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1536,12 +1757,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1558,12 +1779,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1585,7 +1806,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1602,12 +1823,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1624,12 +1845,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1651,7 +1872,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1673,7 +1894,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1690,12 +1911,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1717,7 +1938,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1739,7 +1960,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1761,7 +1982,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1783,7 +2004,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1800,12 +2021,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1822,7 +2043,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1849,7 +2070,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1866,12 +2087,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1893,7 +2114,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1954,12 +2175,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1976,12 +2197,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2003,7 +2224,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2025,7 +2246,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2042,12 +2263,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2064,12 +2285,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2086,12 +2307,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2108,12 +2329,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2130,12 +2351,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2152,12 +2373,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2174,12 +2395,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2196,12 +2417,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2218,12 +2439,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2240,12 +2461,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2262,12 +2483,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2284,12 +2505,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2306,12 +2527,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2328,12 +2549,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2350,12 +2571,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2372,12 +2593,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2615,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2416,12 +2637,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2438,12 +2659,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2460,12 +2681,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2482,12 +2703,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2504,12 +2725,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2526,12 +2747,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2548,7 +2769,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2570,12 +2791,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2597,7 +2818,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2614,12 +2835,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2636,12 +2857,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2663,7 +2884,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2680,12 +2901,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2702,12 +2923,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2724,7 +2945,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2746,12 +2967,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2768,12 +2989,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2790,12 +3011,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2812,7 +3033,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2834,12 +3055,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2856,12 +3077,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2883,7 +3104,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2905,7 +3126,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2922,12 +3143,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2949,7 +3170,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2966,12 +3187,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2988,12 +3209,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3010,12 +3231,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3032,20 +3253,1142 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3084,7 +4427,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3094,7 +4437,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -3120,7 +4463,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_12.xlsx
+++ b/ttl_long/AdHoc_Net_12.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>322</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>228</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>310</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>231</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>438</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>260</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>459</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>458</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>563</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>470</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>536</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>550</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>597</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>724</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>245</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>792</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>743</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>874</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>169</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>842</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>282</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>827</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>934</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>971</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>336</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>963</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1113</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>244</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1204</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>342</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1090</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1177</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>153</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1166</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1280</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1407</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1350</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1327</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1530</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1575</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1522</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1682</t>
         </is>
       </c>
     </row>
@@ -1123,114 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>139</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1376</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1511</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1532</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1565</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1599</t>
+          <t>1549</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1300,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1322,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1344,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1366,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1388,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1410,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1427,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1493,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1515,12 +1413,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1542,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1564,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1608,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1625,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1674,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1691,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1713,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1757,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1784,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1806,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1828,7 +1726,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1845,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1872,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1894,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1916,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1938,7 +1836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1960,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1982,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1999,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2026,7 +1924,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2065,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2092,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2109,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2131,7 +2029,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2153,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2175,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2197,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2219,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2241,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2268,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2285,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2307,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2334,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2351,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2378,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2400,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2417,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2444,7 +2342,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2466,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2488,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2510,7 +2408,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2527,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2554,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2576,7 +2474,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2598,7 +2496,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2615,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2642,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2664,7 +2562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2681,7 +2579,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2703,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2730,7 +2628,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2752,7 +2650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2769,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2796,7 +2694,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2813,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2840,7 +2738,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2862,7 +2760,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2884,7 +2782,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2928,7 +2826,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2950,7 +2848,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2972,7 +2870,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2994,7 +2892,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3016,7 +2914,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3033,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3060,7 +2958,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3082,7 +2980,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3099,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3126,7 +3024,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3148,7 +3046,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3165,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3187,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3236,7 +3134,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3258,7 +3156,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3280,7 +3178,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3297,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3319,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3346,7 +3244,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3363,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3385,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3412,7 +3310,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3434,7 +3332,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3451,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3473,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3500,7 +3398,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3517,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3539,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3561,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3583,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3605,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3627,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3649,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3671,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3693,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3715,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3737,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3759,12 +3657,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3781,7 +3679,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3795,600 +3693,6 @@
         </is>
       </c>
       <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4427,7 +3731,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -4437,7 +3741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -4457,7 +3761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
